--- a/artfynd/A 33875-2021 artfynd.xlsx
+++ b/artfynd/A 33875-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33875-2021 artfynd.xlsx
+++ b/artfynd/A 33875-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2206,10 +2206,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79437369</v>
+        <v>79437336</v>
       </c>
       <c r="B15" t="n">
-        <v>78533</v>
+        <v>78570</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,25 +2218,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456177.428588222</v>
+        <v>456261.3445848088</v>
       </c>
       <c r="R15" t="n">
-        <v>7085543.027184287</v>
+        <v>7085455.951132528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,11 +2302,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2323,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79437336</v>
+        <v>79435838</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
+        <v>89356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,25 +2330,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,13 +2358,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456261.3445848088</v>
+        <v>456167.0470215179</v>
       </c>
       <c r="R16" t="n">
-        <v>7085455.951132528</v>
+        <v>7085337.000852794</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2419,26 +2414,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79435838</v>
+        <v>79435873</v>
       </c>
       <c r="B17" t="n">
-        <v>89356</v>
+        <v>89673</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,25 +2457,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2475,10 +2485,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456167.0470215179</v>
+        <v>456140.8032513115</v>
       </c>
       <c r="R17" t="n">
-        <v>7085337.000852794</v>
+        <v>7085447.504282765</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2562,10 +2572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79435873</v>
+        <v>79437330</v>
       </c>
       <c r="B18" t="n">
-        <v>89673</v>
+        <v>78596</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,25 +2584,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2602,13 +2612,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456140.8032513115</v>
+        <v>456192.2405595645</v>
       </c>
       <c r="R18" t="n">
-        <v>7085447.504282765</v>
+        <v>7085403.611614834</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,40 +2669,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79437330</v>
+        <v>79437374</v>
       </c>
       <c r="B19" t="n">
-        <v>78596</v>
+        <v>89388</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456192.2405595645</v>
+        <v>456170.9767344035</v>
       </c>
       <c r="R19" t="n">
-        <v>7085403.611614834</v>
+        <v>7085302.582621044</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>grov sälg</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79437374</v>
+        <v>79437331</v>
       </c>
       <c r="B20" t="n">
-        <v>89388</v>
+        <v>78596</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2818,25 +2818,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456170.9767344035</v>
+        <v>456249.2789020801</v>
       </c>
       <c r="R20" t="n">
-        <v>7085302.582621044</v>
+        <v>7085476.384176624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>grov sälg</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79437331</v>
+        <v>79437354</v>
       </c>
       <c r="B21" t="n">
-        <v>78596</v>
+        <v>78603</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2939,21 +2939,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456249.2789020801</v>
+        <v>456244.6041358357</v>
       </c>
       <c r="R21" t="n">
-        <v>7085476.384176624</v>
+        <v>7085457.50653425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79437354</v>
+        <v>79436307</v>
       </c>
       <c r="B22" t="n">
-        <v>78603</v>
+        <v>78570</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456244.6041358357</v>
+        <v>456227.6257899638</v>
       </c>
       <c r="R22" t="n">
-        <v>7085457.50653425</v>
+        <v>7085473.602959829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3137,30 +3137,25 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>79436307</v>
+        <v>79437313</v>
       </c>
       <c r="B23" t="n">
-        <v>78570</v>
+        <v>76504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456227.6257899638</v>
+        <v>456180.5772851193</v>
       </c>
       <c r="R23" t="n">
-        <v>7085473.602959829</v>
+        <v>7085547.388361699</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3257,22 +3252,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79437313</v>
+        <v>79435840</v>
       </c>
       <c r="B24" t="n">
-        <v>76504</v>
+        <v>89392</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3285,21 +3280,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3309,13 +3304,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456180.5772851193</v>
+        <v>456140.8032513115</v>
       </c>
       <c r="R24" t="n">
-        <v>7085547.388361699</v>
+        <v>7085447.504282765</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3365,26 +3360,41 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79435840</v>
+        <v>79436308</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
+        <v>93044</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3393,25 +3403,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3421,13 +3431,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456140.8032513115</v>
+        <v>456171.0533641183</v>
       </c>
       <c r="R25" t="n">
-        <v>7085447.504282765</v>
+        <v>7085339.588106645</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3477,41 +3487,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>79436308</v>
+        <v>79437334</v>
       </c>
       <c r="B26" t="n">
-        <v>93044</v>
+        <v>78596</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3524,21 +3519,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3548,10 +3543,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456171.0533641183</v>
+        <v>456178.3106115148</v>
       </c>
       <c r="R26" t="n">
-        <v>7085339.588106645</v>
+        <v>7085543.014844382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3605,25 +3600,30 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>79437334</v>
+        <v>79435903</v>
       </c>
       <c r="B27" t="n">
-        <v>78596</v>
+        <v>73678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456178.3106115148</v>
+        <v>456163.1728765632</v>
       </c>
       <c r="R27" t="n">
-        <v>7085543.014844382</v>
+        <v>7085375.382860185</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3716,31 +3716,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79435903</v>
+        <v>79436042</v>
       </c>
       <c r="B28" t="n">
-        <v>73678</v>
+        <v>76863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3749,25 +3744,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3777,13 +3772,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456163.1728765632</v>
+        <v>455764.3191481924</v>
       </c>
       <c r="R28" t="n">
-        <v>7085375.382860185</v>
+        <v>7085557.204025372</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3807,7 +3802,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3817,7 +3812,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3833,6 +3828,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3842,17 +3852,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79436042</v>
+        <v>79437345</v>
       </c>
       <c r="B29" t="n">
-        <v>76863</v>
+        <v>78570</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3861,25 +3871,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3889,10 +3899,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455764.3191481924</v>
+        <v>456197.1176868261</v>
       </c>
       <c r="R29" t="n">
-        <v>7085557.204025372</v>
+        <v>7085500.020756101</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3919,7 +3929,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3929,7 +3939,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -3946,37 +3956,27 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>79437345</v>
+        <v>79437344</v>
       </c>
       <c r="B30" t="n">
         <v>78570</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456197.1176868261</v>
+        <v>456240.9467338301</v>
       </c>
       <c r="R30" t="n">
-        <v>7085500.020756101</v>
+        <v>7085448.30638066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4093,10 +4093,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>79437344</v>
+        <v>79437375</v>
       </c>
       <c r="B31" t="n">
-        <v>78570</v>
+        <v>73507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4105,25 +4105,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456240.9467338301</v>
+        <v>456170.9767344035</v>
       </c>
       <c r="R31" t="n">
-        <v>7085448.30638066</v>
+        <v>7085302.582621044</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>grov sälg</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79437375</v>
+        <v>79435855</v>
       </c>
       <c r="B32" t="n">
-        <v>73507</v>
+        <v>73685</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4222,25 +4222,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456170.9767344035</v>
+        <v>456163.1728765632</v>
       </c>
       <c r="R32" t="n">
-        <v>7085302.582621044</v>
+        <v>7085375.382860185</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4307,30 +4307,40 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>grov sälg</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>79435855</v>
+        <v>79435911</v>
       </c>
       <c r="B33" t="n">
-        <v>73685</v>
+        <v>89410</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4339,25 +4349,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4367,10 +4377,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456163.1728765632</v>
+        <v>456278.1214801408</v>
       </c>
       <c r="R33" t="n">
-        <v>7085375.382860185</v>
+        <v>7085204.161412235</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4426,17 +4436,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4454,10 +4464,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>79435911</v>
+        <v>79437364</v>
       </c>
       <c r="B34" t="n">
-        <v>89410</v>
+        <v>89388</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4470,21 +4480,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4494,13 +4504,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456278.1214801408</v>
+        <v>456256.3304489632</v>
       </c>
       <c r="R34" t="n">
-        <v>7085204.161412235</v>
+        <v>7085286.410611292</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4550,41 +4560,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>79437364</v>
+        <v>79437365</v>
       </c>
       <c r="B35" t="n">
-        <v>89388</v>
+        <v>78533</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4593,25 +4588,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>229748</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4621,10 +4616,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456256.3304489632</v>
+        <v>456244.6041358357</v>
       </c>
       <c r="R35" t="n">
-        <v>7085286.410611292</v>
+        <v>7085457.50653425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4677,6 +4672,11 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4693,7 +4693,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>79437365</v>
+        <v>79437367</v>
       </c>
       <c r="B36" t="n">
         <v>78533</v>
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456244.6041358357</v>
+        <v>456206.0896373163</v>
       </c>
       <c r="R36" t="n">
-        <v>7085457.50653425</v>
+        <v>7085479.190371729</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>79437367</v>
+        <v>79437353</v>
       </c>
       <c r="B37" t="n">
-        <v>78533</v>
+        <v>78603</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229748</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456206.0896373163</v>
+        <v>456249.6593677456</v>
       </c>
       <c r="R37" t="n">
-        <v>7085479.190371729</v>
+        <v>7085282.538741915</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4927,10 +4927,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>79437353</v>
+        <v>79435885</v>
       </c>
       <c r="B38" t="n">
-        <v>78603</v>
+        <v>76863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4939,25 +4939,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4967,13 +4967,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456249.6593677456</v>
+        <v>456202.7727709666</v>
       </c>
       <c r="R38" t="n">
-        <v>7085282.538741915</v>
+        <v>7085273.501592995</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5024,30 +5024,40 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>79435885</v>
+        <v>79435850</v>
       </c>
       <c r="B39" t="n">
-        <v>76863</v>
+        <v>78596</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5056,25 +5066,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>498</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5084,10 +5094,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456202.7727709666</v>
+        <v>456143.7913634988</v>
       </c>
       <c r="R39" t="n">
-        <v>7085273.501592995</v>
+        <v>7085566.405092322</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5140,21 +5150,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5171,10 +5166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>79435850</v>
+        <v>79435844</v>
       </c>
       <c r="B40" t="n">
-        <v>78596</v>
+        <v>90074</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5187,21 +5182,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5211,10 +5206,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456143.7913634988</v>
+        <v>456125.0497337686</v>
       </c>
       <c r="R40" t="n">
-        <v>7085566.405092322</v>
+        <v>7085456.535621062</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5267,6 +5262,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5283,10 +5293,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79435844</v>
+        <v>79437324</v>
       </c>
       <c r="B41" t="n">
-        <v>90074</v>
+        <v>78596</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5299,21 +5309,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5323,13 +5333,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456125.0497337686</v>
+        <v>455846.4529545773</v>
       </c>
       <c r="R41" t="n">
-        <v>7085456.535621062</v>
+        <v>7085500.979336833</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5380,40 +5390,30 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>79437324</v>
+        <v>79437351</v>
       </c>
       <c r="B42" t="n">
-        <v>78596</v>
+        <v>78569</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5422,25 +5422,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455846.4529545773</v>
+        <v>456243.0805592343</v>
       </c>
       <c r="R42" t="n">
-        <v>7085500.979336833</v>
+        <v>7085285.273983967</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>79437351</v>
+        <v>79437333</v>
       </c>
       <c r="B43" t="n">
-        <v>78569</v>
+        <v>78596</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5539,25 +5539,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456243.0805592343</v>
+        <v>456185.2656570955</v>
       </c>
       <c r="R43" t="n">
-        <v>7085285.273983967</v>
+        <v>7085504.151277401</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5644,10 +5644,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>79437333</v>
+        <v>79436305</v>
       </c>
       <c r="B44" t="n">
-        <v>78596</v>
+        <v>96354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5660,21 +5660,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456185.2656570955</v>
+        <v>456225.2628025854</v>
       </c>
       <c r="R44" t="n">
-        <v>7085504.151277401</v>
+        <v>7085493.900417267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5741,30 +5741,25 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>79436305</v>
+        <v>79435912</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
+        <v>89410</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5773,25 +5768,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5801,13 +5796,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456225.2628025854</v>
+        <v>456173.542896258</v>
       </c>
       <c r="R45" t="n">
-        <v>7085493.900417267</v>
+        <v>7085296.819473872</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5857,26 +5852,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>79435912</v>
+        <v>79435849</v>
       </c>
       <c r="B46" t="n">
-        <v>89410</v>
+        <v>78596</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5885,25 +5895,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5913,10 +5923,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456173.542896258</v>
+        <v>456101.8016950651</v>
       </c>
       <c r="R46" t="n">
-        <v>7085296.819473872</v>
+        <v>7085434.393946561</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5969,21 +5979,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6000,10 +5995,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>79435849</v>
+        <v>79436306</v>
       </c>
       <c r="B47" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6012,25 +6007,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6040,13 +6035,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456101.8016950651</v>
+        <v>456142.2592155717</v>
       </c>
       <c r="R47" t="n">
-        <v>7085434.393946561</v>
+        <v>7085362.45917053</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6100,19 +6095,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>79436306</v>
+        <v>79437337</v>
       </c>
       <c r="B48" t="n">
         <v>78570</v>
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456142.2592155717</v>
+        <v>455851.7637905481</v>
       </c>
       <c r="R48" t="n">
-        <v>7085362.45917053</v>
+        <v>7085502.226070778</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6209,25 +6204,30 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>79437337</v>
+        <v>79435871</v>
       </c>
       <c r="B49" t="n">
-        <v>78570</v>
+        <v>93056</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6236,25 +6236,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>2813</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6264,13 +6264,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455851.7637905481</v>
+        <v>456171.9389396965</v>
       </c>
       <c r="R49" t="n">
-        <v>7085502.226070778</v>
+        <v>7085308.296392513</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6320,31 +6320,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>79435871</v>
+        <v>79437343</v>
       </c>
       <c r="B50" t="n">
-        <v>93056</v>
+        <v>78570</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6353,25 +6348,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6381,13 +6376,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456171.9389396965</v>
+        <v>456244.8262937459</v>
       </c>
       <c r="R50" t="n">
-        <v>7085308.296392513</v>
+        <v>7085283.927922516</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6437,26 +6432,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>79437343</v>
+        <v>79435917</v>
       </c>
       <c r="B51" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456244.8262937459</v>
+        <v>456173.542896258</v>
       </c>
       <c r="R51" t="n">
-        <v>7085283.927922516</v>
+        <v>7085296.819473872</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6549,31 +6549,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>79435917</v>
+        <v>79437318</v>
       </c>
       <c r="B52" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6586,21 +6581,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6610,13 +6605,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456173.542896258</v>
+        <v>456182.3413292455</v>
       </c>
       <c r="R52" t="n">
-        <v>7085296.819473872</v>
+        <v>7085547.363683905</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6670,19 +6665,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>79437318</v>
+        <v>79437317</v>
       </c>
       <c r="B53" t="n">
         <v>73693</v>
@@ -6722,10 +6717,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456182.3413292455</v>
+        <v>456203.8434372738</v>
       </c>
       <c r="R53" t="n">
-        <v>7085547.363683905</v>
+        <v>7085255.423579955</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6794,10 +6789,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79437317</v>
+        <v>79436304</v>
       </c>
       <c r="B54" t="n">
-        <v>73693</v>
+        <v>78596</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6806,25 +6801,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456203.8434372738</v>
+        <v>456219.7366528938</v>
       </c>
       <c r="R54" t="n">
-        <v>7085255.423579955</v>
+        <v>7085477.237473203</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6894,22 +6889,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>79436304</v>
+        <v>79436061</v>
       </c>
       <c r="B55" t="n">
-        <v>78596</v>
+        <v>89410</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6918,25 +6913,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6946,10 +6941,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456219.7366528938</v>
+        <v>455777.2638905769</v>
       </c>
       <c r="R55" t="n">
-        <v>7085477.237473203</v>
+        <v>7085568.034293007</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6976,7 +6971,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -6986,7 +6981,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7002,26 +6997,41 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>79436061</v>
+        <v>79435848</v>
       </c>
       <c r="B56" t="n">
-        <v>89410</v>
+        <v>78596</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7030,25 +7040,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7058,13 +7068,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455777.2638905769</v>
+        <v>456173.542896258</v>
       </c>
       <c r="R56" t="n">
-        <v>7085568.034293007</v>
+        <v>7085296.819473872</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7088,7 +7098,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7098,7 +7108,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7114,21 +7124,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7138,17 +7133,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79435848</v>
+        <v>79435869</v>
       </c>
       <c r="B57" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7157,25 +7152,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7257,10 +7252,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>79435869</v>
+        <v>79465190</v>
       </c>
       <c r="B58" t="n">
-        <v>78570</v>
+        <v>77668</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7269,25 +7264,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7297,13 +7292,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456173.542896258</v>
+        <v>456291.0687427432</v>
       </c>
       <c r="R58" t="n">
-        <v>7085296.819473872</v>
+        <v>7085278.436212774</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7353,23 +7348,28 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79465190</v>
+        <v>79465189</v>
       </c>
       <c r="B59" t="n">
         <v>77668</v>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456291.0687427432</v>
+        <v>456243.7846159392</v>
       </c>
       <c r="R59" t="n">
-        <v>7085278.436212774</v>
+        <v>7085177.765924375</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>björk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>79465189</v>
+        <v>79465188</v>
       </c>
       <c r="B60" t="n">
         <v>77668</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456243.7846159392</v>
+        <v>456156.4463807809</v>
       </c>
       <c r="R60" t="n">
-        <v>7085177.765924375</v>
+        <v>7085367.547148879</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>79465188</v>
+        <v>82123674</v>
       </c>
       <c r="B61" t="n">
-        <v>77668</v>
+        <v>73473</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7619,21 +7619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1249</v>
+        <v>98</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7643,10 +7643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456156.4463807809</v>
+        <v>456170.9828971688</v>
       </c>
       <c r="R61" t="n">
-        <v>7085367.547148879</v>
+        <v>7085303.023091642</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>grov sälg</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7713,17 +7713,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
+          <t>Linda Johannesson, Isak Vahlström, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>82123674</v>
+        <v>89604421</v>
       </c>
       <c r="B62" t="n">
-        <v>73473</v>
+        <v>90319</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7732,38 +7732,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>98</v>
+        <v>4769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Veksjörun, Jmt</t>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456170.9828971688</v>
+        <v>456456.0617167632</v>
       </c>
       <c r="R62" t="n">
-        <v>7085303.023091642</v>
+        <v>7085659.84216597</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -7816,31 +7816,30 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>grov sälg</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>89604421</v>
+        <v>89604418</v>
       </c>
       <c r="B63" t="n">
-        <v>90319</v>
+        <v>78596</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7853,21 +7852,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4769</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7877,10 +7876,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456456.0617167632</v>
+        <v>456432.9035791646</v>
       </c>
       <c r="R63" t="n">
-        <v>7085659.84216597</v>
+        <v>7085739.013709916</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7953,10 +7952,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>89604418</v>
+        <v>89604422</v>
       </c>
       <c r="B64" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7965,25 +7964,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7993,10 +7992,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456432.9035791646</v>
+        <v>456482.0760057283</v>
       </c>
       <c r="R64" t="n">
-        <v>7085739.013709916</v>
+        <v>7085532.171961885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8069,10 +8068,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>89604422</v>
+        <v>89604430</v>
       </c>
       <c r="B65" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8085,21 +8084,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8109,10 +8108,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456482.0760057283</v>
+        <v>456654.8024139004</v>
       </c>
       <c r="R65" t="n">
-        <v>7085532.171961885</v>
+        <v>7085231.969409176</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8185,10 +8184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>89604430</v>
+        <v>89604436</v>
       </c>
       <c r="B66" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8201,21 +8200,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8225,10 +8224,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456654.8024139004</v>
+        <v>456438.1525085681</v>
       </c>
       <c r="R66" t="n">
-        <v>7085231.969409176</v>
+        <v>7085735.857238096</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8301,10 +8300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>89604436</v>
+        <v>89604416</v>
       </c>
       <c r="B67" t="n">
-        <v>89410</v>
+        <v>78570</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8317,21 +8316,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8341,10 +8340,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456438.1525085681</v>
+        <v>456432.9035791646</v>
       </c>
       <c r="R67" t="n">
-        <v>7085735.857238096</v>
+        <v>7085739.013709916</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8410,122 +8409,6 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>89604416</v>
-      </c>
-      <c r="B68" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>456432.9035791646</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7085739.013709916</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 33875-2021 artfynd.xlsx
+++ b/artfynd/A 33875-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79435856</v>
+        <v>82123674</v>
       </c>
       <c r="B2" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>492</v>
+        <v>98</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456137.5711899451</v>
+        <v>456171</v>
       </c>
       <c r="R2" t="n">
-        <v>7085405.698276078</v>
+        <v>7085303</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +743,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,67 +757,52 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>grov sälg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79435904</v>
+        <v>79437313</v>
       </c>
       <c r="B3" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456142.9093467598</v>
+        <v>456181</v>
       </c>
       <c r="R3" t="n">
-        <v>7085566.417441969</v>
+        <v>7085547</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,19 +845,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,49 +862,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79437370</v>
+        <v>79435855</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456235.6667419327</v>
+        <v>456163</v>
       </c>
       <c r="R4" t="n">
-        <v>7085449.261217624</v>
+        <v>7085375</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,21 +942,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,53 +955,63 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79437368</v>
+        <v>79435856</v>
       </c>
       <c r="B5" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229748</v>
+        <v>492</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456178.3106115148</v>
+        <v>456138</v>
       </c>
       <c r="R5" t="n">
-        <v>7085543.014844382</v>
+        <v>7085406</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,21 +1054,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1123,57 +1068,62 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79437373</v>
+        <v>79435885</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456204.6701195224</v>
+        <v>456203</v>
       </c>
       <c r="R6" t="n">
-        <v>7085251.446950207</v>
+        <v>7085274</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,21 +1166,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,53 +1179,63 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79437321</v>
+        <v>79436042</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456232.573367773</v>
+        <v>455764</v>
       </c>
       <c r="R7" t="n">
-        <v>7085259.427680398</v>
+        <v>7085557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,31 +1291,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79435916</v>
+        <v>79435926</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456167.9044499879</v>
+        <v>455858</v>
       </c>
       <c r="R8" t="n">
-        <v>7085335.226646451</v>
+        <v>7085429</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,19 +1390,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79435895</v>
+        <v>79435873</v>
       </c>
       <c r="B9" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455851.5775578448</v>
+        <v>456141</v>
       </c>
       <c r="R9" t="n">
-        <v>7085489.012759613</v>
+        <v>7085448</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,19 +1502,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,15 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79435898</v>
+        <v>79435895</v>
       </c>
       <c r="B10" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456101.3359776126</v>
+        <v>455852</v>
       </c>
       <c r="R10" t="n">
-        <v>7085432.638318013</v>
+        <v>7085489</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1694,19 +1614,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,15 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79436303</v>
+        <v>79435898</v>
       </c>
       <c r="B11" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456146.2030922453</v>
+        <v>456101</v>
       </c>
       <c r="R11" t="n">
-        <v>7085549.631521768</v>
+        <v>7085433</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,21 +1726,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1844,31 +1739,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79437346</v>
+        <v>79436054</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1900,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455975.7857934998</v>
+        <v>455757</v>
       </c>
       <c r="R12" t="n">
-        <v>7085570.083483324</v>
+        <v>7085550</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,22 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,57 +1852,62 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79435882</v>
+        <v>79437364</v>
       </c>
       <c r="B13" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2017,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456177.1847949281</v>
+        <v>456256</v>
       </c>
       <c r="R13" t="n">
-        <v>7085336.418461666</v>
+        <v>7085286</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,19 +1950,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,49 +1967,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79437332</v>
+        <v>79437374</v>
       </c>
       <c r="B14" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2129,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456242.2698086891</v>
+        <v>456171</v>
       </c>
       <c r="R14" t="n">
-        <v>7085448.28789786</v>
+        <v>7085303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,21 +2047,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2063,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>grov sälg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2206,15 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79437336</v>
+        <v>79435840</v>
       </c>
       <c r="B15" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,13 +2116,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456261.3445848088</v>
+        <v>456141</v>
       </c>
       <c r="R15" t="n">
-        <v>7085455.951132528</v>
+        <v>7085448</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2279,21 +2149,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2302,53 +2162,63 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79435838</v>
+        <v>79435916</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456167.0470215179</v>
+        <v>456168</v>
       </c>
       <c r="R16" t="n">
-        <v>7085337.000852794</v>
+        <v>7085335</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2391,19 +2261,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,15 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79435873</v>
+        <v>79436026</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,37 +2316,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Veksjörun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456140.8032513115</v>
+        <v>455758</v>
       </c>
       <c r="R17" t="n">
-        <v>7085447.504282765</v>
+        <v>7085547</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2515,22 +2373,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,6 +2387,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2565,44 +2414,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79437330</v>
+        <v>79465188</v>
       </c>
       <c r="B18" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2612,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456192.2405595645</v>
+        <v>456156</v>
       </c>
       <c r="R18" t="n">
-        <v>7085403.611614834</v>
+        <v>7085368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2645,21 +2489,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2671,7 +2505,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2682,44 +2516,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79437374</v>
+        <v>79465189</v>
       </c>
       <c r="B19" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2729,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456170.9767344035</v>
+        <v>456244</v>
       </c>
       <c r="R19" t="n">
-        <v>7085302.582621044</v>
+        <v>7085178</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2762,21 +2591,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2788,7 +2607,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>grov sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2799,44 +2618,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79437331</v>
+        <v>79465190</v>
       </c>
       <c r="B20" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2846,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456249.2789020801</v>
+        <v>456291</v>
       </c>
       <c r="R20" t="n">
-        <v>7085476.384176624</v>
+        <v>7085278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,21 +2693,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2905,7 +2709,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björk</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2916,44 +2720,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79437354</v>
+        <v>79435922</v>
       </c>
       <c r="B21" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2963,13 +2762,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456244.6041358357</v>
+        <v>456206</v>
       </c>
       <c r="R21" t="n">
-        <v>7085457.50653425</v>
+        <v>7085161</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2996,59 +2795,55 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79436307</v>
+        <v>79437373</v>
       </c>
       <c r="B22" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3056,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3080,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456227.6257899638</v>
+        <v>456205</v>
       </c>
       <c r="R22" t="n">
-        <v>7085473.602959829</v>
+        <v>7085251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3113,19 +2908,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3140,49 +2925,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>79437313</v>
+        <v>79436034</v>
       </c>
       <c r="B23" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3192,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456180.5772851193</v>
+        <v>455758</v>
       </c>
       <c r="R23" t="n">
-        <v>7085547.388361699</v>
+        <v>7085550</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,22 +3002,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3248,31 +3018,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79435840</v>
+        <v>79435857</v>
       </c>
       <c r="B24" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3304,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456140.8032513115</v>
+        <v>455862</v>
       </c>
       <c r="R24" t="n">
-        <v>7085447.504282765</v>
+        <v>7085445</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3337,21 +3117,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3360,21 +3130,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3391,37 +3146,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79436308</v>
+        <v>79435867</v>
       </c>
       <c r="B25" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3431,13 +3181,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456171.0533641183</v>
+        <v>456211</v>
       </c>
       <c r="R25" t="n">
-        <v>7085339.588106645</v>
+        <v>7085159</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3464,19 +3214,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3491,49 +3231,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>79437334</v>
+        <v>79435869</v>
       </c>
       <c r="B26" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3543,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456178.3106115148</v>
+        <v>456174</v>
       </c>
       <c r="R26" t="n">
-        <v>7085543.014844382</v>
+        <v>7085297</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3576,21 +3311,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3599,58 +3324,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>79435903</v>
+        <v>79436306</v>
       </c>
       <c r="B27" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3660,13 +3375,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456163.1728765632</v>
+        <v>456142</v>
       </c>
       <c r="R27" t="n">
-        <v>7085375.382860185</v>
+        <v>7085362</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3693,19 +3408,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3720,49 +3425,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79436042</v>
+        <v>79436307</v>
       </c>
       <c r="B28" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3772,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455764.3191481924</v>
+        <v>456228</v>
       </c>
       <c r="R28" t="n">
-        <v>7085557.204025372</v>
+        <v>7085474</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3802,22 +3502,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,46 +3518,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79437345</v>
+        <v>79437336</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456197.1176868261</v>
+        <v>456261</v>
       </c>
       <c r="R29" t="n">
-        <v>7085500.020756101</v>
+        <v>7085456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3932,21 +3602,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3955,11 +3615,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3976,15 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>79437344</v>
+        <v>79437337</v>
       </c>
       <c r="B30" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456240.9467338301</v>
+        <v>455852</v>
       </c>
       <c r="R30" t="n">
-        <v>7085448.30638066</v>
+        <v>7085502</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4049,19 +3699,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,37 +3733,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>79437375</v>
+        <v>79437338</v>
       </c>
       <c r="B31" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6428</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4133,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456170.9767344035</v>
+        <v>455869</v>
       </c>
       <c r="R31" t="n">
-        <v>7085302.582621044</v>
+        <v>7085421</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4166,21 +3801,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4189,11 +3814,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>grov sälg</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4210,37 +3830,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79435855</v>
+        <v>79437343</v>
       </c>
       <c r="B32" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4250,13 +3865,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456163.1728765632</v>
+        <v>456245</v>
       </c>
       <c r="R32" t="n">
-        <v>7085375.382860185</v>
+        <v>7085284</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4283,21 +3898,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4307,45 +3912,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>79435911</v>
+        <v>79437344</v>
       </c>
       <c r="B33" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4353,21 +3943,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4377,13 +3967,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456278.1214801408</v>
+        <v>456241</v>
       </c>
       <c r="R33" t="n">
-        <v>7085204.161412235</v>
+        <v>7085448</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4410,21 +4000,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4434,45 +4014,30 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>79437364</v>
+        <v>79437345</v>
       </c>
       <c r="B34" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4480,21 +4045,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4504,10 +4069,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456256.3304489632</v>
+        <v>456197</v>
       </c>
       <c r="R34" t="n">
-        <v>7085286.410611292</v>
+        <v>7085500</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,21 +4102,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4560,6 +4115,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4576,37 +4136,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>79437365</v>
+        <v>79437346</v>
       </c>
       <c r="B35" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4616,10 +4171,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456244.6041358357</v>
+        <v>455976</v>
       </c>
       <c r="R35" t="n">
-        <v>7085457.50653425</v>
+        <v>7085570</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4649,19 +4204,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4693,50 +4238,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>79437367</v>
+        <v>89604416</v>
       </c>
       <c r="B36" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Veksjörun, Jmt</t>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456206.0896373163</v>
+        <v>456433</v>
       </c>
       <c r="R36" t="n">
-        <v>7085479.190371729</v>
+        <v>7085739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4763,22 +4303,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4789,71 +4319,65 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>79437353</v>
+        <v>89604422</v>
       </c>
       <c r="B37" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Veksjörun, Jmt</t>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456249.6593677456</v>
+        <v>456482</v>
       </c>
       <c r="R37" t="n">
-        <v>7085282.538741915</v>
+        <v>7085532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4880,22 +4404,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4906,58 +4420,52 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>79435885</v>
+        <v>79436308</v>
       </c>
       <c r="B38" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>498</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4967,13 +4475,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456202.7727709666</v>
+        <v>456171</v>
       </c>
       <c r="R38" t="n">
-        <v>7085273.501592995</v>
+        <v>7085340</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5000,21 +4508,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5023,46 +4521,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>79435850</v>
+        <v>79435871</v>
       </c>
       <c r="B39" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5070,21 +4548,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>2813</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5094,10 +4572,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456143.7913634988</v>
+        <v>456172</v>
       </c>
       <c r="R39" t="n">
-        <v>7085566.405092322</v>
+        <v>7085308</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5127,19 +4605,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5169,12 +4637,7 @@
         <v>79435844</v>
       </c>
       <c r="B40" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5206,10 +4669,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456125.0497337686</v>
+        <v>456125</v>
       </c>
       <c r="R40" t="n">
-        <v>7085456.535621062</v>
+        <v>7085457</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5239,19 +4702,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5293,15 +4746,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79437324</v>
+        <v>89604421</v>
       </c>
       <c r="B41" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5309,34 +4757,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Veksjörun, Jmt</t>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455846.4529545773</v>
+        <v>456456</v>
       </c>
       <c r="R41" t="n">
-        <v>7085500.979336833</v>
+        <v>7085660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5363,22 +4811,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5389,58 +4827,52 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>79437351</v>
+        <v>79435838</v>
       </c>
       <c r="B42" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5450,13 +4882,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456243.0805592343</v>
+        <v>456167</v>
       </c>
       <c r="R42" t="n">
-        <v>7085285.273983967</v>
+        <v>7085337</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5483,21 +4915,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5507,57 +4929,62 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>79437333</v>
+        <v>79435917</v>
       </c>
       <c r="B43" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5567,13 +4994,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456185.2656570955</v>
+        <v>456174</v>
       </c>
       <c r="R43" t="n">
-        <v>7085504.151277401</v>
+        <v>7085297</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5600,21 +5027,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5623,71 +5040,61 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>79436305</v>
+        <v>89604430</v>
       </c>
       <c r="B44" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Veksjörun, Jmt</t>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456225.2628025854</v>
+        <v>456655</v>
       </c>
       <c r="R44" t="n">
-        <v>7085493.900417267</v>
+        <v>7085232</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5714,22 +5121,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5744,49 +5141,48 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>79435912</v>
+        <v>79437375</v>
       </c>
       <c r="B45" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6428</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5796,13 +5192,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456173.542896258</v>
+        <v>456171</v>
       </c>
       <c r="R45" t="n">
-        <v>7085296.819473872</v>
+        <v>7085303</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5829,21 +5225,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5853,45 +5239,30 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>grov sälg</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>79435849</v>
+        <v>79435903</v>
       </c>
       <c r="B46" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5899,21 +5270,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5923,10 +5294,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456101.8016950651</v>
+        <v>456163</v>
       </c>
       <c r="R46" t="n">
-        <v>7085434.393946561</v>
+        <v>7085375</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5956,19 +5327,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5995,37 +5356,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>79436306</v>
+        <v>79435904</v>
       </c>
       <c r="B47" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6035,13 +5391,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456142.2592155717</v>
+        <v>456143</v>
       </c>
       <c r="R47" t="n">
-        <v>7085362.45917053</v>
+        <v>7085566</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6068,19 +5424,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6095,27 +5441,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>79437337</v>
+        <v>79435833</v>
       </c>
       <c r="B48" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6123,21 +5464,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6147,13 +5488,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455851.7637905481</v>
+        <v>456122</v>
       </c>
       <c r="R48" t="n">
-        <v>7085502.226070778</v>
+        <v>7085584</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6180,21 +5521,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6204,57 +5535,62 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>79435871</v>
+        <v>79436303</v>
       </c>
       <c r="B49" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2813</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6264,13 +5600,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456171.9389396965</v>
+        <v>456146</v>
       </c>
       <c r="R49" t="n">
-        <v>7085308.296392513</v>
+        <v>7085550</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6297,19 +5633,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6324,27 +5650,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>79437343</v>
+        <v>79437317</v>
       </c>
       <c r="B50" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6352,21 +5673,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6376,10 +5697,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456244.8262937459</v>
+        <v>456204</v>
       </c>
       <c r="R50" t="n">
-        <v>7085283.927922516</v>
+        <v>7085255</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,21 +5730,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6432,11 +5743,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6453,15 +5759,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>79435917</v>
+        <v>79437318</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6469,21 +5770,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6493,13 +5794,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456173.542896258</v>
+        <v>456182</v>
       </c>
       <c r="R51" t="n">
-        <v>7085296.819473872</v>
+        <v>7085547</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6526,19 +5827,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6553,27 +5844,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>79437318</v>
+        <v>79437321</v>
       </c>
       <c r="B52" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6605,10 +5891,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456182.3413292455</v>
+        <v>456233</v>
       </c>
       <c r="R52" t="n">
-        <v>7085547.363683905</v>
+        <v>7085259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6638,19 +5924,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6677,15 +5953,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>79437317</v>
+        <v>79437351</v>
       </c>
       <c r="B53" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6693,21 +5964,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6717,10 +5988,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456203.8434372738</v>
+        <v>456243</v>
       </c>
       <c r="R53" t="n">
-        <v>7085255.423579955</v>
+        <v>7085285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6750,21 +6021,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6773,6 +6034,11 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6789,15 +6055,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79436304</v>
+        <v>79437356</v>
       </c>
       <c r="B54" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6805,21 +6066,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6829,10 +6090,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456219.7366528938</v>
+        <v>455987</v>
       </c>
       <c r="R54" t="n">
-        <v>7085477.237473203</v>
+        <v>7085596</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6862,21 +6123,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6885,53 +6136,53 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>79436061</v>
+        <v>79435847</v>
       </c>
       <c r="B55" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6941,13 +6192,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455777.2638905769</v>
+        <v>456211</v>
       </c>
       <c r="R55" t="n">
-        <v>7085568.034293007</v>
+        <v>7085159</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6971,22 +6222,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6997,21 +6238,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7021,7 +6247,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber, Viktor Gårdman</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7031,12 +6257,7 @@
         <v>79435848</v>
       </c>
       <c r="B56" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,10 +6289,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456173.542896258</v>
+        <v>456174</v>
       </c>
       <c r="R56" t="n">
-        <v>7085296.819473872</v>
+        <v>7085297</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7101,19 +6322,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7140,37 +6351,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79435869</v>
+        <v>79435849</v>
       </c>
       <c r="B57" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7180,10 +6386,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456173.542896258</v>
+        <v>456102</v>
       </c>
       <c r="R57" t="n">
-        <v>7085296.819473872</v>
+        <v>7085434</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7213,19 +6419,9 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2019-08-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7252,37 +6448,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>79465190</v>
+        <v>79435850</v>
       </c>
       <c r="B58" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7292,13 +6483,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456291.0687427432</v>
+        <v>456144</v>
       </c>
       <c r="R58" t="n">
-        <v>7085278.436212774</v>
+        <v>7085566</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7325,21 +6516,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7348,58 +6529,48 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>björk</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79465189</v>
+        <v>79436304</v>
       </c>
       <c r="B59" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7409,10 +6580,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456243.7846159392</v>
+        <v>456220</v>
       </c>
       <c r="R59" t="n">
-        <v>7085177.765924375</v>
+        <v>7085477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7442,21 +6613,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7465,58 +6626,48 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>79465188</v>
+        <v>79437324</v>
       </c>
       <c r="B60" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7526,10 +6677,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456156.4463807809</v>
+        <v>455846</v>
       </c>
       <c r="R60" t="n">
-        <v>7085367.547148879</v>
+        <v>7085501</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7559,21 +6710,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7585,7 +6726,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7596,44 +6737,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>82123674</v>
+        <v>79437325</v>
       </c>
       <c r="B61" t="n">
-        <v>73473</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>98</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7643,10 +6779,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456170.9828971688</v>
+        <v>455870</v>
       </c>
       <c r="R61" t="n">
-        <v>7085303.023091642</v>
+        <v>7085420</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7676,21 +6812,11 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7699,11 +6825,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>grov sälg</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7713,22 +6834,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Tore Dahlberg</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>89604421</v>
+        <v>79437330</v>
       </c>
       <c r="B62" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7736,34 +6852,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4769</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+          <t>Veksjörun, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456456.0617167632</v>
+        <v>456192</v>
       </c>
       <c r="R62" t="n">
-        <v>7085659.84216597</v>
+        <v>7085404</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7790,22 +6906,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7816,35 +6922,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>89604418</v>
+        <v>79437331</v>
       </c>
       <c r="B63" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7872,14 +6974,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+          <t>Veksjörun, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456432.9035791646</v>
+        <v>456249</v>
       </c>
       <c r="R63" t="n">
-        <v>7085739.013709916</v>
+        <v>7085476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7906,22 +7008,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7932,70 +7024,66 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>89604422</v>
+        <v>79437332</v>
       </c>
       <c r="B64" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+          <t>Veksjörun, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456482.0760057283</v>
+        <v>456242</v>
       </c>
       <c r="R64" t="n">
-        <v>7085532.171961885</v>
+        <v>7085448</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8022,22 +7110,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8048,70 +7126,66 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>89604430</v>
+        <v>79437333</v>
       </c>
       <c r="B65" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+          <t>Veksjörun, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456654.8024139004</v>
+        <v>456185</v>
       </c>
       <c r="R65" t="n">
-        <v>7085231.969409176</v>
+        <v>7085504</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8138,22 +7212,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8164,70 +7228,66 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>89604436</v>
+        <v>79437334</v>
       </c>
       <c r="B66" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+          <t>Veksjörun, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456438.1525085681</v>
+        <v>456178</v>
       </c>
       <c r="R66" t="n">
-        <v>7085735.857238096</v>
+        <v>7085543</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8254,22 +7314,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8280,57 +7330,53 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>89604416</v>
+        <v>89604418</v>
       </c>
       <c r="B67" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8340,10 +7386,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456432.9035791646</v>
+        <v>456433</v>
       </c>
       <c r="R67" t="n">
-        <v>7085739.013709916</v>
+        <v>7085739</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8373,19 +7419,9 @@
           <t>2020-10-07</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8413,6 +7449,1128 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>79435882</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>456177</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7085336</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>79437353</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>456250</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7085283</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>79437354</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>456245</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7085458</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>89604459</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>S Lill-Veksjön,Lill-Bakvattnet-Tretjärnarna, nor, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>456541</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7085470</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>79435930</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>456181</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7085261</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>79436305</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>456225</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7085494</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>79435899</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>455863</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7085429</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>79437365</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>456245</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7085458</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>79437367</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>456206</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7085479</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>79437368</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>456178</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7085543</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>79437369</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Veksjörun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>456177</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7085543</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
